--- a/notification_configs/PA_backup_01_daily_status_reminders.xlsx
+++ b/notification_configs/PA_backup_01_daily_status_reminders.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -576,6 +576,594 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>VENDOR_01111_20250911</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>thunderblunder018@gmail.com</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gopal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>01111</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MEdiatek</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MTK34710</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Please submit your daily attendance status - Gopal</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>vendor_01111</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2025-09-11 10:17:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VENDOR_EMP001_20250911</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>john.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EMP001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TechCorp Solutions</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Please submit your daily attendance status - John Smith</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>vendor_emp001</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2025-09-11 10:17:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VENDOR_EMP002_20250911</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>jane.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Jane Wilson</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EMP002</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TechCorp Solutions</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Please submit your daily attendance status - Jane Wilson</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>vendor_emp002</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2025-09-11 10:17:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VENDOR_EMP003_20250911</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mike.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mike Rodriguez</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>InfraCorp Ltd</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>M002</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Please submit your daily attendance status - Mike Rodriguez</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>vendor_emp003</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2025-09-11 10:17:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VENDOR_EMP004_20250911</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sarah.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sarah Parker</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>QualityCorp Inc</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>M003</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Please submit your daily attendance status - Sarah Parker</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>vendor_emp004</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2025-09-11 10:17:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VENDOR_EMP005_20250911</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>david.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>David Kim</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EMP005</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TechCorp Solutions</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Please submit your daily attendance status - David Kim</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>vendor_emp005</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2025-09-11 10:17:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
